--- a/data/acompanhamento/trilhas/Associate Data Scientist  in Python.xlsx
+++ b/data/acompanhamento/trilhas/Associate Data Scientist  in Python.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,20 +446,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>xp_curso</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ordem_para_assistir</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>tipo_trilha</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>data_final_para_assistir</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>obrigatoriedade_curso</t>
         </is>
@@ -476,19 +481,20 @@
           <t>Introduction to Python</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C2" t="n">
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -503,19 +509,20 @@
           <t>Intermediate Python</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C3" t="n">
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>7400</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -530,19 +537,20 @@
           <t>Data Manipulation with pandas</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C4" t="n">
+        <v>4</v>
       </c>
       <c r="D4" t="n">
+        <v>4850</v>
+      </c>
+      <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -557,19 +565,20 @@
           <t>Joining Data with pandas</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C5" t="n">
+        <v>4</v>
       </c>
       <c r="D5" t="n">
+        <v>4050</v>
+      </c>
+      <c r="E5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -584,19 +593,20 @@
           <t>Introduction to Statistics in Python</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C6" t="n">
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>4250</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -611,19 +621,20 @@
           <t>Introduction to Data Visualization with Matplotlib</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C7" t="n">
+        <v>4</v>
       </c>
       <c r="D7" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -638,19 +649,20 @@
           <t>Introduction to Data Visualization with Seaborn</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C8" t="n">
+        <v>4</v>
       </c>
       <c r="D8" t="n">
+        <v>3700</v>
+      </c>
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -665,19 +677,20 @@
           <t>Introduction to Functions in Python</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3 hr</t>
-        </is>
+      <c r="C9" t="n">
+        <v>3</v>
       </c>
       <c r="D9" t="n">
+        <v>3550</v>
+      </c>
+      <c r="E9" t="n">
         <v>7</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -692,19 +705,20 @@
           <t>Python Toolbox</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C10" t="n">
+        <v>4</v>
       </c>
       <c r="D10" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E10" t="n">
         <v>8</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -719,19 +733,20 @@
           <t>Exploratory Data Analysis in Python</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C11" t="n">
+        <v>4</v>
       </c>
       <c r="D11" t="n">
+        <v>4150</v>
+      </c>
+      <c r="E11" t="n">
         <v>9</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -746,19 +761,20 @@
           <t>Working with Categorical Data in Python</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C12" t="n">
+        <v>4</v>
       </c>
       <c r="D12" t="n">
+        <v>4200</v>
+      </c>
+      <c r="E12" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="n">
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -773,19 +789,20 @@
           <t>Data Communication Concepts</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3 hr</t>
-        </is>
+      <c r="C13" t="n">
+        <v>3</v>
       </c>
       <c r="D13" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E13" t="n">
         <v>11</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="n">
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -800,19 +817,20 @@
           <t>Introduction to Importing Data in Python</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3 hr</t>
-        </is>
+      <c r="C14" t="n">
+        <v>3</v>
       </c>
       <c r="D14" t="n">
+        <v>3900</v>
+      </c>
+      <c r="E14" t="n">
         <v>12</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="n">
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -827,19 +845,20 @@
           <t>Cleaning Data in Python</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C15" t="n">
+        <v>4</v>
       </c>
       <c r="D15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E15" t="n">
         <v>13</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -854,19 +873,20 @@
           <t>Working with Dates and Times in Python</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C16" t="n">
+        <v>4</v>
       </c>
       <c r="D16" t="n">
+        <v>4100</v>
+      </c>
+      <c r="E16" t="n">
         <v>14</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="n">
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -881,19 +901,20 @@
           <t>Writing Functions in Python</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C17" t="n">
+        <v>4</v>
       </c>
       <c r="D17" t="n">
+        <v>3650</v>
+      </c>
+      <c r="E17" t="n">
         <v>15</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -908,19 +929,20 @@
           <t>Introduction to Regression with statsmodels in Python</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C18" t="n">
+        <v>4</v>
       </c>
       <c r="D18" t="n">
+        <v>4150</v>
+      </c>
+      <c r="E18" t="n">
         <v>16</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -935,19 +957,20 @@
           <t>Sampling in Python</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C19" t="n">
+        <v>4</v>
       </c>
       <c r="D19" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E19" t="n">
         <v>17</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="n">
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -962,19 +985,20 @@
           <t>Hypothesis Testing in Python</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C20" t="n">
+        <v>4</v>
       </c>
       <c r="D20" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E20" t="n">
         <v>18</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="n">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -989,19 +1013,20 @@
           <t>Experimental Design in Python</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C21" t="n">
+        <v>4</v>
       </c>
       <c r="D21" t="n">
+        <v>3700</v>
+      </c>
+      <c r="E21" t="n">
         <v>19</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="n">
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1016,19 +1041,20 @@
           <t>Supervised Learning with scikit-learn</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C22" t="n">
+        <v>4</v>
       </c>
       <c r="D22" t="n">
+        <v>4050</v>
+      </c>
+      <c r="E22" t="n">
         <v>20</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="n">
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1043,19 +1069,20 @@
           <t>Unsupervised Learning in Python</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>4 hr</t>
-        </is>
+      <c r="C23" t="n">
+        <v>4</v>
       </c>
       <c r="D23" t="n">
+        <v>4150</v>
+      </c>
+      <c r="E23" t="n">
         <v>21</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="n">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1070,19 +1097,20 @@
           <t>Machine Learning with Tree-Based Models in Python</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>5 hr</t>
-        </is>
+      <c r="C24" t="n">
+        <v>5</v>
       </c>
       <c r="D24" t="n">
+        <v>4650</v>
+      </c>
+      <c r="E24" t="n">
         <v>22</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="n">
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
         <v>1</v>
       </c>
     </row>
